--- a/artfynd/A 44301-2020 artfynd.xlsx
+++ b/artfynd/A 44301-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121645891</v>
+        <v>121645888</v>
       </c>
       <c r="B2" t="n">
-        <v>58213</v>
+        <v>58216</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -708,26 +708,12 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>eDNA</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -772,6 +758,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-05-08</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Samlingsprov från lokalen.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121645905</v>
+        <v>121645870</v>
       </c>
       <c r="B3" t="n">
-        <v>58213</v>
+        <v>57510</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,25 +802,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208249</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -837,27 +828,14 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>funnen död</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Brännås, Vg</t>
@@ -867,10 +845,10 @@
         <v>337484</v>
       </c>
       <c r="R3" t="n">
-        <v>6404724</v>
+        <v>6404684</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -908,7 +886,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -927,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121645870</v>
+        <v>121645905</v>
       </c>
       <c r="B4" t="n">
-        <v>57509</v>
+        <v>58216</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,25 +916,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>208249</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -965,14 +942,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>funnen död</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Brännås, Vg</t>
@@ -982,10 +972,10 @@
         <v>337484</v>
       </c>
       <c r="R4" t="n">
-        <v>6404684</v>
+        <v>6404724</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1023,6 +1013,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 44301-2020 artfynd.xlsx
+++ b/artfynd/A 44301-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121645888</v>
+        <v>121645870</v>
       </c>
       <c r="B2" t="n">
-        <v>58216</v>
+        <v>57510</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,48 +687,53 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208249</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>eDNA</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Brännås, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>337471</v>
+        <v>337484</v>
       </c>
       <c r="R2" t="n">
-        <v>6404727</v>
+        <v>6404684</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,17 +757,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Samlingsprov från lokalen.</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,7 +771,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -783,17 +782,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jonas Örnborg</t>
+          <t>Jonas Örnborg, Tove Lawenius</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121645870</v>
+        <v>121645888</v>
       </c>
       <c r="B3" t="n">
-        <v>57510</v>
+        <v>58216</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,53 +801,48 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>208249</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>eDNA</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Brännås, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>337484</v>
+        <v>337471</v>
       </c>
       <c r="R3" t="n">
-        <v>6404684</v>
+        <v>6404727</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,12 +866,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2024-05-08</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Samlingsprov från lokalen.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,6 +885,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -897,7 +897,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jonas Örnborg, Tove Lawenius</t>
+          <t>Jonas Örnborg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 44301-2020 artfynd.xlsx
+++ b/artfynd/A 44301-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1030,6 +1030,601 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122565585</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56289</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100092</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Nyctalus noctula</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Stamsjön 2, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>337593</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6404650</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lerum</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lerum</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-06-18</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Filip Myllyaho, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122565617</v>
+      </c>
+      <c r="B6" t="n">
+        <v>56275</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Stamsjön 2, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>337593</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6404650</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Lerum</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lerum</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Filip Myllyaho, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122565574</v>
+      </c>
+      <c r="B7" t="n">
+        <v>56294</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Stamsjön 2, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>337593</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6404650</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Lerum</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lerum</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Filip Myllyaho, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>122565564</v>
+      </c>
+      <c r="B8" t="n">
+        <v>56296</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>206002</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Brunlångöra</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Plecotus auritus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Stamsjön 2, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>337593</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6404650</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Lerum</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lerum</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-06-18</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Filip Myllyaho, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122565603</v>
+      </c>
+      <c r="B9" t="n">
+        <v>56282</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>205992</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Myotis daubentonii</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Stamsjön 2, Vg</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>337593</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6404650</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Lerum</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Lerum</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Filip Myllyaho, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 44301-2020 artfynd.xlsx
+++ b/artfynd/A 44301-2020 artfynd.xlsx
@@ -1032,10 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122565585</v>
+        <v>122565564</v>
       </c>
       <c r="B5" t="n">
-        <v>56289</v>
+        <v>56296</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1044,30 +1044,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100092</v>
+        <v>206002</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1151,7 +1151,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122565617</v>
+        <v>122565619</v>
       </c>
       <c r="B6" t="n">
         <v>56275</v>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1270,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122565574</v>
+        <v>122565585</v>
       </c>
       <c r="B7" t="n">
-        <v>56294</v>
+        <v>56289</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1286,26 +1286,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1357,12 +1357,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1389,10 +1389,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122565564</v>
+        <v>122565603</v>
       </c>
       <c r="B8" t="n">
-        <v>56296</v>
+        <v>56282</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1401,30 +1401,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>206002</v>
+        <v>205992</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1508,10 +1508,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122565603</v>
+        <v>122565575</v>
       </c>
       <c r="B9" t="n">
-        <v>56282</v>
+        <v>56294</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1524,26 +1524,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 44301-2020 artfynd.xlsx
+++ b/artfynd/A 44301-2020 artfynd.xlsx
@@ -1151,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122565619</v>
+        <v>122565574</v>
       </c>
       <c r="B6" t="n">
-        <v>56275</v>
+        <v>56294</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,30 +1163,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>61</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1270,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122565585</v>
+        <v>122565617</v>
       </c>
       <c r="B7" t="n">
-        <v>56289</v>
+        <v>56275</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1282,30 +1282,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1357,12 +1357,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1389,10 +1389,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122565603</v>
+        <v>122565585</v>
       </c>
       <c r="B8" t="n">
-        <v>56282</v>
+        <v>56289</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1405,26 +1405,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1508,10 +1508,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122565575</v>
+        <v>122565603</v>
       </c>
       <c r="B9" t="n">
-        <v>56294</v>
+        <v>56282</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1524,26 +1524,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 44301-2020 artfynd.xlsx
+++ b/artfynd/A 44301-2020 artfynd.xlsx
@@ -1032,10 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122565564</v>
+        <v>122565575</v>
       </c>
       <c r="B5" t="n">
-        <v>56296</v>
+        <v>56294</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1044,30 +1044,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>206002</v>
+        <v>205995</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1151,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122565574</v>
+        <v>122565585</v>
       </c>
       <c r="B6" t="n">
-        <v>56294</v>
+        <v>56289</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,26 +1167,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1270,7 +1270,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122565617</v>
+        <v>122565619</v>
       </c>
       <c r="B7" t="n">
         <v>56275</v>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1357,12 +1357,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1389,10 +1389,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122565585</v>
+        <v>122565603</v>
       </c>
       <c r="B8" t="n">
-        <v>56289</v>
+        <v>56282</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1405,26 +1405,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1508,10 +1508,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122565603</v>
+        <v>122565564</v>
       </c>
       <c r="B9" t="n">
-        <v>56282</v>
+        <v>56296</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1520,30 +1520,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>205992</v>
+        <v>206002</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 44301-2020 artfynd.xlsx
+++ b/artfynd/A 44301-2020 artfynd.xlsx
@@ -1032,7 +1032,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122565575</v>
+        <v>122565574</v>
       </c>
       <c r="B5" t="n">
         <v>56294</v>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>61</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122565585</v>
+        <v>122565603</v>
       </c>
       <c r="B6" t="n">
-        <v>56289</v>
+        <v>56282</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,26 +1167,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1389,10 +1389,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122565603</v>
+        <v>122565564</v>
       </c>
       <c r="B8" t="n">
-        <v>56282</v>
+        <v>56296</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1401,30 +1401,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>205992</v>
+        <v>206002</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1508,10 +1508,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122565564</v>
+        <v>122565585</v>
       </c>
       <c r="B9" t="n">
-        <v>56296</v>
+        <v>56289</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1520,30 +1520,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>206002</v>
+        <v>100092</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">

--- a/artfynd/A 44301-2020 artfynd.xlsx
+++ b/artfynd/A 44301-2020 artfynd.xlsx
@@ -1032,10 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122565574</v>
+        <v>122565575</v>
       </c>
       <c r="B5" t="n">
-        <v>56294</v>
+        <v>56295</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122565603</v>
+        <v>122565585</v>
       </c>
       <c r="B6" t="n">
-        <v>56282</v>
+        <v>56290</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,26 +1167,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1270,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122565619</v>
+        <v>122565617</v>
       </c>
       <c r="B7" t="n">
-        <v>56275</v>
+        <v>56276</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1357,12 +1357,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1392,7 +1392,7 @@
         <v>122565564</v>
       </c>
       <c r="B8" t="n">
-        <v>56296</v>
+        <v>56297</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1508,10 +1508,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122565585</v>
+        <v>122565603</v>
       </c>
       <c r="B9" t="n">
-        <v>56289</v>
+        <v>56283</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1524,26 +1524,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 44301-2020 artfynd.xlsx
+++ b/artfynd/A 44301-2020 artfynd.xlsx
@@ -1032,10 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122565575</v>
+        <v>122565617</v>
       </c>
       <c r="B5" t="n">
-        <v>56295</v>
+        <v>56276</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1044,30 +1044,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122565585</v>
+        <v>122565564</v>
       </c>
       <c r="B6" t="n">
-        <v>56290</v>
+        <v>56297</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,30 +1163,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100092</v>
+        <v>206002</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1270,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122565617</v>
+        <v>122565575</v>
       </c>
       <c r="B7" t="n">
-        <v>56276</v>
+        <v>56295</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1282,30 +1282,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1357,12 +1357,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1389,10 +1389,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122565564</v>
+        <v>122565603</v>
       </c>
       <c r="B8" t="n">
-        <v>56297</v>
+        <v>56283</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1401,30 +1401,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>206002</v>
+        <v>205992</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1508,10 +1508,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122565603</v>
+        <v>122565585</v>
       </c>
       <c r="B9" t="n">
-        <v>56283</v>
+        <v>56290</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1524,26 +1524,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 44301-2020 artfynd.xlsx
+++ b/artfynd/A 44301-2020 artfynd.xlsx
@@ -1032,7 +1032,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122565617</v>
+        <v>122565619</v>
       </c>
       <c r="B5" t="n">
         <v>56276</v>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1270,7 +1270,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122565575</v>
+        <v>122565574</v>
       </c>
       <c r="B7" t="n">
         <v>56295</v>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>61</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1357,12 +1357,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 44301-2020 artfynd.xlsx
+++ b/artfynd/A 44301-2020 artfynd.xlsx
@@ -1032,10 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122565603</v>
+        <v>122565574</v>
       </c>
       <c r="B5" t="n">
-        <v>56377</v>
+        <v>56389</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,26 +1048,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>61</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1151,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122565564</v>
+        <v>122565619</v>
       </c>
       <c r="B6" t="n">
-        <v>56391</v>
+        <v>56370</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,26 +1167,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>206002</v>
+        <v>205998</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1389,10 +1389,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122565617</v>
+        <v>122565603</v>
       </c>
       <c r="B8" t="n">
-        <v>56370</v>
+        <v>56377</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1401,30 +1401,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1508,10 +1508,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122565574</v>
+        <v>122565564</v>
       </c>
       <c r="B9" t="n">
-        <v>56389</v>
+        <v>56391</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1520,30 +1520,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>205995</v>
+        <v>206002</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 44301-2020 artfynd.xlsx
+++ b/artfynd/A 44301-2020 artfynd.xlsx
@@ -1032,10 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122565574</v>
+        <v>122565617</v>
       </c>
       <c r="B5" t="n">
-        <v>56389</v>
+        <v>56370</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1044,30 +1044,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1151,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122565619</v>
+        <v>122565603</v>
       </c>
       <c r="B6" t="n">
-        <v>56370</v>
+        <v>56377</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,30 +1163,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1270,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122565585</v>
+        <v>122565575</v>
       </c>
       <c r="B7" t="n">
-        <v>56384</v>
+        <v>56389</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1286,26 +1286,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1389,10 +1389,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122565603</v>
+        <v>122565564</v>
       </c>
       <c r="B8" t="n">
-        <v>56377</v>
+        <v>56391</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1401,30 +1401,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>205992</v>
+        <v>206002</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1508,10 +1508,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122565564</v>
+        <v>122565585</v>
       </c>
       <c r="B9" t="n">
-        <v>56391</v>
+        <v>56384</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1520,30 +1520,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>206002</v>
+        <v>100092</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">

--- a/artfynd/A 44301-2020 artfynd.xlsx
+++ b/artfynd/A 44301-2020 artfynd.xlsx
@@ -1032,10 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122565617</v>
+        <v>122565585</v>
       </c>
       <c r="B5" t="n">
-        <v>56370</v>
+        <v>56384</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1044,30 +1044,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122565603</v>
+        <v>122565564</v>
       </c>
       <c r="B6" t="n">
-        <v>56377</v>
+        <v>56391</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,30 +1163,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>205992</v>
+        <v>206002</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1270,7 +1270,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122565575</v>
+        <v>122565574</v>
       </c>
       <c r="B7" t="n">
         <v>56389</v>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>61</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1357,12 +1357,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1389,10 +1389,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122565564</v>
+        <v>122565619</v>
       </c>
       <c r="B8" t="n">
-        <v>56391</v>
+        <v>56370</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1405,26 +1405,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>206002</v>
+        <v>205998</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1508,10 +1508,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122565585</v>
+        <v>122565603</v>
       </c>
       <c r="B9" t="n">
-        <v>56384</v>
+        <v>56377</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1524,26 +1524,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 44301-2020 artfynd.xlsx
+++ b/artfynd/A 44301-2020 artfynd.xlsx
@@ -1389,7 +1389,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122565619</v>
+        <v>122565617</v>
       </c>
       <c r="B8" t="n">
         <v>56370</v>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 44301-2020 artfynd.xlsx
+++ b/artfynd/A 44301-2020 artfynd.xlsx
@@ -1032,10 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122565585</v>
+        <v>122565564</v>
       </c>
       <c r="B5" t="n">
-        <v>56384</v>
+        <v>56391</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1044,30 +1044,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100092</v>
+        <v>206002</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1151,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122565564</v>
+        <v>122565585</v>
       </c>
       <c r="B6" t="n">
-        <v>56391</v>
+        <v>56384</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,30 +1163,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>206002</v>
+        <v>100092</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">

--- a/artfynd/A 44301-2020 artfynd.xlsx
+++ b/artfynd/A 44301-2020 artfynd.xlsx
@@ -1032,10 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122565564</v>
+        <v>122565585</v>
       </c>
       <c r="B5" t="n">
-        <v>56391</v>
+        <v>56384</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1044,30 +1044,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>206002</v>
+        <v>100092</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1151,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122565585</v>
+        <v>122565564</v>
       </c>
       <c r="B6" t="n">
-        <v>56384</v>
+        <v>56391</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,30 +1163,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100092</v>
+        <v>206002</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
